--- a/output/pdf_financials_xlsx/ORV.xlsx
+++ b/output/pdf_financials_xlsx/ORV.xlsx
@@ -2027,7 +2027,7 @@
         <v>-1.592</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>0.867</v>
+        <v>-0.867</v>
       </c>
       <c r="M23" s="3" t="n">
         <v>-13.719</v>
@@ -6579,7 +6579,7 @@
         <v>-1.592</v>
       </c>
       <c r="L99" s="3" t="n">
-        <v>0.867</v>
+        <v>-0.867</v>
       </c>
       <c r="M99" s="3" t="n">
         <v>-13.719</v>
@@ -32952,7 +32952,7 @@
         <v>-1.592</v>
       </c>
       <c r="O271" s="5" t="n">
-        <v>0.867</v>
+        <v>-0.867</v>
       </c>
       <c r="P271" s="5" t="n">
         <v>-13.719</v>

--- a/output/pdf_financials_xlsx/ORV.xlsx
+++ b/output/pdf_financials_xlsx/ORV.xlsx
@@ -2013,15 +2013,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I23" s="3" t="n">
+        <v>-11.097</v>
+      </c>
+      <c r="J23" s="3" t="n">
+        <v>-5.266</v>
       </c>
       <c r="K23" s="3" t="n">
         <v>-1.592</v>
@@ -2032,10 +2028,8 @@
       <c r="M23" s="3" t="n">
         <v>-13.719</v>
       </c>
-      <c r="N23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N23" s="3" t="n">
+        <v>2.708</v>
       </c>
       <c r="O23" s="1" t="inlineStr">
         <is>
@@ -4043,7 +4037,7 @@
         <v>0</v>
       </c>
       <c r="C56" s="3" t="n">
-        <v>0</v>
+        <v>254.125</v>
       </c>
       <c r="D56" s="3" t="n">
         <v>0</v>
@@ -4085,7 +4079,7 @@
         <v>0</v>
       </c>
       <c r="O56" s="3" t="n">
-        <v>0</v>
+        <v>339.45</v>
       </c>
       <c r="P56" s="3" t="n">
         <v>0</v>
@@ -4101,7 +4095,7 @@
         <v>0</v>
       </c>
       <c r="C57" s="3" t="n">
-        <v>0</v>
+        <v>30.702</v>
       </c>
       <c r="D57" s="3" t="n">
         <v>0</v>
@@ -4703,40 +4697,34 @@
         <v>0</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>8.15</v>
+      </c>
+      <c r="F67" s="3" t="n">
+        <v>5.296</v>
+      </c>
+      <c r="G67" s="3" t="n">
+        <v>7.992</v>
+      </c>
+      <c r="H67" s="3" t="n">
+        <v>6.827</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>6.54</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>4.702</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>5.517</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>5.729</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>5.377</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>5.043</v>
       </c>
       <c r="O67" s="3" t="n">
         <v>0</v>
@@ -4901,22 +4889,22 @@
         <v>0</v>
       </c>
       <c r="K70" s="3" t="n">
-        <v>0</v>
+        <v>1.037</v>
       </c>
       <c r="L70" s="3" t="n">
-        <v>0</v>
+        <v>1.519</v>
       </c>
       <c r="M70" s="3" t="n">
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="N70" s="3" t="n">
-        <v>0</v>
+        <v>1.004</v>
       </c>
       <c r="O70" s="3" t="n">
-        <v>0</v>
+        <v>0.605</v>
       </c>
       <c r="P70" s="3" t="n">
-        <v>0</v>
+        <v>0.244</v>
       </c>
     </row>
     <row r="71">
@@ -4959,22 +4947,22 @@
         <v>0</v>
       </c>
       <c r="K71" s="3" t="n">
-        <v>0</v>
+        <v>1.037</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>0</v>
+        <v>1.519</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>0</v>
+        <v>1.004</v>
       </c>
       <c r="O71" s="3" t="n">
-        <v>0</v>
+        <v>0.605</v>
       </c>
       <c r="P71" s="3" t="n">
-        <v>0</v>
+        <v>0.244</v>
       </c>
     </row>
     <row r="72">
@@ -5191,22 +5179,22 @@
         <v>11.781</v>
       </c>
       <c r="K75" s="3" t="n">
-        <v>15.615</v>
+        <v>14.578</v>
       </c>
       <c r="L75" s="3" t="n">
-        <v>13.958</v>
+        <v>12.439</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>11.044</v>
+        <v>10.824</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>10.896</v>
+        <v>9.891999999999999</v>
       </c>
       <c r="O75" s="3" t="n">
-        <v>8.789999999999999</v>
+        <v>8.185</v>
       </c>
       <c r="P75" s="3" t="n">
-        <v>19.723</v>
+        <v>19.479</v>
       </c>
     </row>
     <row r="76">
@@ -5489,22 +5477,22 @@
         </is>
       </c>
       <c r="K80" s="3" t="n">
-        <v>0.02564391591049991</v>
+        <v>0.04025531195401003</v>
       </c>
       <c r="L80" s="3" t="n">
-        <v>0.0003421825543927685</v>
+        <v>0.02199948672616841</v>
       </c>
       <c r="M80" s="3" t="n">
-        <v>0.00136576722896903</v>
+        <v>0.005426156288066147</v>
       </c>
       <c r="N80" s="3" t="n">
-        <v>0.004844498665110769</v>
+        <v>0.02259587333580862</v>
       </c>
       <c r="O80" s="3" t="n">
-        <v>0.006081619787514138</v>
+        <v>0.01729924165167894</v>
       </c>
       <c r="P80" s="3" t="n">
-        <v>0.002117849500319883</v>
+        <v>0.007500716980299587</v>
       </c>
     </row>
     <row r="81">
@@ -6565,15 +6553,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I99" s="3" t="n">
+        <v>-11.097</v>
+      </c>
+      <c r="J99" s="3" t="n">
+        <v>-5.266</v>
       </c>
       <c r="K99" s="3" t="n">
         <v>-1.592</v>
@@ -6584,10 +6568,8 @@
       <c r="M99" s="3" t="n">
         <v>-13.719</v>
       </c>
-      <c r="N99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N99" s="3" t="n">
+        <v>2.708</v>
       </c>
       <c r="O99" s="1" t="inlineStr">
         <is>
@@ -7302,25 +7284,25 @@
         </is>
       </c>
       <c r="I110" s="3" t="n">
-        <v>0</v>
+        <v>0.719</v>
       </c>
       <c r="J110" s="3" t="n">
-        <v>0</v>
+        <v>0.542</v>
       </c>
       <c r="K110" s="3" t="n">
-        <v>0</v>
+        <v>0.43</v>
       </c>
       <c r="L110" s="3" t="n">
-        <v>0</v>
+        <v>0.448</v>
       </c>
       <c r="M110" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N110" s="3" t="n">
-        <v>0</v>
+        <v>0.765</v>
       </c>
       <c r="O110" s="3" t="n">
-        <v>0</v>
+        <v>0.903</v>
       </c>
       <c r="P110" s="3" t="n">
         <v>0</v>
@@ -10728,7 +10710,11 @@
           <t>Lease liabilities (note 19)</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>-</t>
@@ -16006,7 +15992,11 @@
           <t>Lease liabilities (note 20)</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr"/>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E81" t="inlineStr">
         <is>
           <t>-</t>
@@ -20189,7 +20179,11 @@
           <t>Lease liabilities (note 18)</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr"/>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E128" t="inlineStr">
         <is>
           <t>-</t>
@@ -31120,7 +31114,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D251" t="inlineStr"/>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E251" t="inlineStr">
         <is>
           <t>-</t>
@@ -31565,7 +31563,11 @@
           <t>Net income(loss) (1) $</t>
         </is>
       </c>
-      <c r="D256" t="inlineStr"/>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E256" t="inlineStr">
         <is>
           <t>-</t>
@@ -36522,7 +36524,11 @@
           <t>Net loss from continuing operations $</t>
         </is>
       </c>
-      <c r="D311" t="inlineStr"/>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E311" t="inlineStr">
         <is>
           <t>-</t>
